--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/aysen.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1185,7 +1185,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1078779-14-CM26</t>
+          <t>1233615-339-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1210,12 +1210,12 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,13 +1240,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>4101.34</v>
+        <v>1623.76</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1233615-339-CM26</t>
+          <t>1078779-14-CM26</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>61.607.800-3</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,7 +1301,7 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>1623.76</v>
+        <v>4101.34</v>
       </c>
     </row>
     <row r="15">
@@ -2095,6 +2095,67 @@
       </c>
       <c r="M27" s="2" t="n">
         <v>757.79</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>1233615-1307-CM26</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>61.980.950-5</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Aysén</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>1726.36</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/aysen.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2713-1116-CM25</t>
+          <t>3791-212-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>6850.66</v>
+        <v>11752.58</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2713-1118-CM25</t>
+          <t>2713-1116-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>19307.75</v>
+        <v>6850.66</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>1057062-687-CM25</t>
+          <t>2713-1118-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -651,7 +651,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3600.23</v>
+        <v>19307.75</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>657-189-CM25</t>
+          <t>1057062-687-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -712,7 +712,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.823.000-7</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION XI REGION</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3219.66</v>
+        <v>3600.23</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4649-261-CM25</t>
+          <t>657-189-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.823.000-7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION XI REGION</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>5094.39</v>
+        <v>3219.66</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>1057062-693-CM25</t>
+          <t>4649-261-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -874,28 +874,28 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3273.33</v>
+        <v>5094.39</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1182705-20-CM26</t>
+          <t>1057062-693-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>65.199.131-5</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA DE LA REGIÓN DE AYSÉN DEL GENERAL CARLOS I</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,13 +935,13 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>6028.9</v>
+        <v>3273.33</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1485465-4-CM26</t>
+          <t>1182705-20-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -956,22 +956,22 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>69.253.500-6</t>
+          <t>65.199.131-5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. Municipalidad de O'Higgins </t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA DE LA REGIÓN DE AYSÉN DEL GENERAL CARLOS I</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,13 +996,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>10142.91</v>
+        <v>6028.9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1233615-335-CM26</t>
+          <t>1485465-4-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1012,27 +1012,27 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>69.253.500-6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t xml:space="preserve">I. Municipalidad de O'Higgins </t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,13 +1057,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2000.99</v>
+        <v>10142.91</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1233615-336-CM26</t>
+          <t>1233615-335-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,13 +1118,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>4665.34</v>
+        <v>2000.99</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1233615-337-CM26</t>
+          <t>1233615-336-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,13 +1179,13 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>428.4</v>
+        <v>4665.34</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1233615-339-CM26</t>
+          <t>1233615-337-CM26</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,7 +1240,7 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>1623.76</v>
+        <v>428.4</v>
       </c>
     </row>
     <row r="14">
@@ -1307,7 +1307,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5038-28-CM26</t>
+          <t>1233615-339-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1317,27 +1317,27 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1347,12 +1347,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K15" t="inlineStr"/>
@@ -1362,13 +1362,13 @@
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>8341.780000000001</v>
+        <v>1623.76</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>4609-148-CM26</t>
+          <t>5038-28-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1383,22 +1383,22 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2026-04-02</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1408,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>76.330.984-3</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,13 +1423,13 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8155.9</v>
+        <v>8341.780000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>1233615-618-CM26</t>
+          <t>4609-148-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1444,7 +1444,7 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2026-04-07</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>4101.45</v>
+        <v>8155.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>3797-344-CM26</t>
+          <t>1233615-618-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>abr-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2026-04-17</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1515,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1530,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,13 +1545,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>9400.620000000001</v>
+        <v>4101.45</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5038-41-CM26</t>
+          <t>3797-344-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1561,27 +1561,27 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-05-20</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1606,13 +1606,13 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>10374.29</v>
+        <v>9400.620000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>3791-632-CM26</t>
+          <t>5038-41-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1627,22 +1627,22 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2026-06-01</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>69.253.100-0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1652,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.075.901-5</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,13 +1667,13 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>1551.17</v>
+        <v>10374.29</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>418-1763-CM26</t>
+          <t>3791-632-CM26</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1688,22 +1688,22 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-06-02</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,13 +1728,13 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>70871.58</v>
+        <v>1551.17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>3797-410-CM26</t>
+          <t>418-1763-CM26</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1749,22 +1749,22 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1774,12 +1774,12 @@
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
@@ -1789,13 +1789,13 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>1064</v>
+        <v>70871.58</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>1233615-995-CM26</t>
+          <t>3797-410-CM26</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1810,7 +1810,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-06-10</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1820,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1835,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1850,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>69475.17999999999</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>418-2089-CM26</t>
+          <t>1233615-995-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,27 +1866,27 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1896,12 +1896,12 @@
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>77.700.780-7</t>
         </is>
       </c>
       <c r="K24" t="inlineStr"/>
@@ -1911,13 +1911,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>10169.55</v>
+        <v>69475.17999999999</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>1057062-288-CM26</t>
+          <t>418-2089-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1942,12 +1942,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>61.602.279-2</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1957,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1972,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>957.12</v>
+        <v>10169.55</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>3797-501-CM26</t>
+          <t>1057062-288-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1993,22 +1993,22 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2018,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2033,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>637</v>
+        <v>957.12</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1428-51-CM26</t>
+          <t>3797-501-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2054,22 +2054,22 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>60.701.004-8</t>
+          <t>69.254.500-1</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2079,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2094,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>757.79</v>
+        <v>637</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1233615-1307-CM26</t>
+          <t>1428-51-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,27 +2110,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>60.701.004-8</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,6 +2155,67 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
+        <v>757.79</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>1233615-1307-CM26</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>61.980.950-5</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Aysén</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="n">
         <v>1726.36</v>
       </c>
     </row>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/aysen.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/aysen.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aysén" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Aysén" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M29"/>
+  <dimension ref="A1:M47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>3791-212-CM25</t>
+          <t>1233615-111-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -529,7 +529,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>11752.58</v>
+        <v>7593.39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2713-1116-CM25</t>
+          <t>1233615-112-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-02-07</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>6850.66</v>
+        <v>7347.06</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2713-1118-CM25</t>
+          <t>3791-212-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.240.100-K</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>19307.75</v>
+        <v>11752.58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>1057062-687-CM25</t>
+          <t>3951-120-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-04-08</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>61.974.700-3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>CONSULTORIO GENERAL URBANO VICTOR DOMINGO SILVA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>3600.23</v>
+        <v>3531.92</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>657-189-CM25</t>
+          <t>907-72-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,27 +768,27 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-05-02</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>61.823.000-7</t>
+          <t>61.308.000-7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>SERVICIO DE VIVIENDA Y URBANIZACION XI REGION</t>
+          <t>SERVICIO AGRICOLA Y GANADERO</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>3219.66</v>
+        <v>2760.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>4649-261-CM25</t>
+          <t>3791-444-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +829,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -844,12 +844,12 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.240.200-6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE CISNES</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>5094.39</v>
+        <v>3277.86</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>1057062-693-CM25</t>
+          <t>2713-453-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -905,12 +905,12 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,12 +920,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
@@ -935,28 +935,28 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3273.33</v>
+        <v>4863.86</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>1182705-20-CM26</t>
+          <t>2713-452-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-01-26</t>
+          <t>2025-05-22</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -966,12 +966,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.199.131-5</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>CENTRO DE FORMACIÓN TÉCNICA DE LA REGIÓN DE AYSÉN DEL GENERAL CARLOS I</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -981,12 +981,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -996,43 +996,43 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>6028.9</v>
+        <v>6250.57</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>1485465-4-CM26</t>
+          <t>1195-272-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>ene-2026</t>
+          <t>may-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-01-30</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.253.500-6</t>
+          <t>69.240.300-2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. Municipalidad de O'Higgins </t>
+          <t>I MUNICIPALIDAD DE COYHAIQUE</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1042,12 +1042,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1057,28 +1057,28 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>10142.91</v>
+        <v>6892.38</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>1233615-335-CM26</t>
+          <t>4609-245-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-06-10</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>69.240.400-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1103,12 +1103,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>ESPEX INGENIERIA LIMITADA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>77.683.370-3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1118,28 +1118,28 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2000.99</v>
+        <v>2656.08</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>1233615-336-CM26</t>
+          <t>1182705-117-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-06-17</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1149,12 +1149,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>65.199.131-5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA DE LA REGIÓN DE AYSÉN DEL GENERAL CARLOS I</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1164,12 +1164,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1179,43 +1179,43 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>4665.34</v>
+        <v>4472.02</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>1233615-337-CM26</t>
+          <t>4140-110-CM25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2025-06-18</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>69.253.000-4</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>I MUNICIPALIDAD DE LAGO VERDE</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1225,12 +1225,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1240,28 +1240,28 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>428.4</v>
+        <v>13417.11</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>1078779-14-CM26</t>
+          <t>1057062-264-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1271,12 +1271,12 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.607.800-3</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1286,12 +1286,12 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1301,28 +1301,28 @@
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>4101.34</v>
+        <v>8584.66</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>1233615-339-CM26</t>
+          <t>1233615-1085-CM25</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-03-23</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1347,58 +1347,62 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>76.423.634-3</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>1623.76</v>
+        <v>132268.08</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>5038-28-CM26</t>
+          <t>1182705-227-CM25</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-04-02</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>65.199.131-5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA DE LA REGIÓN DE AYSÉN DEL GENERAL CARLOS I</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1408,12 +1412,12 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K16" t="inlineStr"/>
@@ -1423,28 +1427,28 @@
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>8341.780000000001</v>
+        <v>16074.04</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>4609-148-CM26</t>
+          <t>1233615-1456-CM25</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>oct-2025</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-04-07</t>
+          <t>2025-10-29</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1454,12 +1458,12 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>69.240.400-9</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1469,12 +1473,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>77.168.105-0</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K17" t="inlineStr"/>
@@ -1484,28 +1488,28 @@
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>8155.9</v>
+        <v>2332.4</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>1233615-618-CM26</t>
+          <t>2713-1118-CM25</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>abr-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-04-17</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1515,12 +1519,12 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1530,12 +1534,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1545,28 +1549,28 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4101.45</v>
+        <v>19307.75</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>3797-344-CM26</t>
+          <t>2713-1116-CM25</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-05-20</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1576,12 +1580,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>69.240.100-K</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>I MUNICIPALIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1591,12 +1595,12 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K19" t="inlineStr"/>
@@ -1606,43 +1610,43 @@
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>9400.620000000001</v>
+        <v>6850.66</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>5038-41-CM26</t>
+          <t>1057062-687-CM25</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.253.100-0</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1652,12 +1656,12 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K20" t="inlineStr"/>
@@ -1667,28 +1671,28 @@
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>10374.29</v>
+        <v>3600.23</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>3791-632-CM26</t>
+          <t>657-189-CM25</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026-06-02</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1698,12 +1702,12 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>69.240.200-6</t>
+          <t>61.823.000-7</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CISNES</t>
+          <t>SERVICIO DE VIVIENDA Y URBANIZACION XI REGION</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -1713,12 +1717,12 @@
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K21" t="inlineStr"/>
@@ -1728,43 +1732,43 @@
         </is>
       </c>
       <c r="M21" s="2" t="n">
-        <v>1551.17</v>
+        <v>3219.66</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>418-1763-CM26</t>
+          <t>4649-261-CM25</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -1789,28 +1793,28 @@
         </is>
       </c>
       <c r="M22" s="2" t="n">
-        <v>70871.58</v>
+        <v>5094.39</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>3797-410-CM26</t>
+          <t>1057062-693-CM25</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2239-5-LR25</t>
+          <t>2239-1-LR24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026-06-10</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1820,12 +1824,12 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>61.980.520-8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>UNIVERSIDAD DE AYSEN</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -1835,12 +1839,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K23" t="inlineStr"/>
@@ -1850,13 +1854,13 @@
         </is>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1064</v>
+        <v>3273.33</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>1233615-995-CM26</t>
+          <t>1182705-20-CM26</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1866,12 +1870,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1881,12 +1885,12 @@
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>61.980.950-5</t>
+          <t>65.199.131-5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Aysén</t>
+          <t>CENTRO DE FORMACIÓN TÉCNICA DE LA REGIÓN DE AYSÉN DEL GENERAL CARLOS I</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -1911,13 +1915,13 @@
         </is>
       </c>
       <c r="M24" s="2" t="n">
-        <v>69475.17999999999</v>
+        <v>6028.9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>418-2089-CM26</t>
+          <t>1485465-4-CM26</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1927,12 +1931,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>ene-2026</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-01-30</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1942,12 +1946,12 @@
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>61.602.279-2</t>
+          <t>69.253.500-6</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+          <t xml:space="preserve">I. Municipalidad de O'Higgins </t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1957,12 +1961,12 @@
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
@@ -1972,13 +1976,13 @@
         </is>
       </c>
       <c r="M25" s="2" t="n">
-        <v>10169.55</v>
+        <v>10142.91</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1057062-288-CM26</t>
+          <t>1233615-335-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1988,27 +1992,27 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026-07-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>61.980.520-8</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE AYSEN</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,12 +2022,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2033,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>957.12</v>
+        <v>2000.99</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>3797-501-CM26</t>
+          <t>1233615-336-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2049,12 +2053,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026-07-15</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -2064,12 +2068,12 @@
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>69.254.500-1</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE COCHRANE</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2079,12 +2083,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2094,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>637</v>
+        <v>4665.34</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1428-51-CM26</t>
+          <t>1233615-337-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2110,27 +2114,27 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>60.701.004-8</t>
+          <t>61.980.950-5</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>Servicio Local de Educación Pública Aysén</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -2140,12 +2144,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2155,13 +2159,13 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>757.79</v>
+        <v>428.4</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>1233615-1307-CM26</t>
+          <t>1233615-339-CM26</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2171,12 +2175,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026-08-06</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -2201,12 +2205,12 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>77.168.105-0</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -2216,7 +2220,1105 @@
         </is>
       </c>
       <c r="M29" s="2" t="n">
+        <v>1623.76</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>1078779-14-CM26</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>61.607.800-3</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>SERVICIO DE SALUD AYSEN CARLOS IBANEZ DEL CAMPO</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Clevertec</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>76.330.984-3</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>4101.34</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>5038-28-CM26</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>2026-04-02</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>69.253.100-0</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>Clevertec</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>76.330.984-3</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>8341.780000000001</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>4609-148-CM26</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2026-04-07</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>69.240.400-9</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CHILE CHICO</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>77.168.105-0</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>8155.9</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>1233615-618-CM26</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>abr-2026</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>61.980.950-5</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Aysén</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>LECHNER S.A</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>4101.45</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>3797-344-CM26</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>69.254.500-1</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>9400.620000000001</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>5038-41-CM26</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>69.253.100-0</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD RIO IBANEZ</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>10374.29</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>3791-632-CM26</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>2026-06-02</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>69.240.200-6</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE CISNES</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>76.799.430-3</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>1551.17</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>418-1763-CM26</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>61.602.279-2</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>70871.58</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>3797-410-CM26</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>2026-06-10</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>69.254.500-1</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>1233615-995-CM26</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>61.980.950-5</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Aysén</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>69475.17999999999</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>418-2089-CM26</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>61.602.279-2</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE SALUD HOSPITAL DE PUERTO AYSEN</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>96.523.180-3</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>10169.55</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>1057062-288-CM26</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>2026-07-01</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>61.980.520-8</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE AYSEN</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>PC FACTORY</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>957.12</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>3797-501-CM26</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>2026-07-15</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>69.254.500-1</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE COCHRANE</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>NET NOW S.A.</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>78.112.170-3</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>1428-51-CM26</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>2026-07-24</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>60.701.004-8</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Servicio Nacional de Pesca y Acuicultura</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>77.727.285-3</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>757.79</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>1233615-1301-CM26</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>61.980.950-5</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Aysén</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>PRODATA S.A</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>4930.77</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>1233615-1307-CM26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>61.980.950-5</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Aysén</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="n">
         <v>1726.36</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>1233615-1316-CM26</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>2026-08-06</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>61.980.950-5</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Servicio Local de Educación Pública Aysén</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>PRODATA S.A</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>79.808.810-6</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>3505.74</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>1182705-156-CM26</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>65.199.131-5</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>CENTRO DE FORMACIÓN TÉCNICA DE LA REGIÓN DE AYSÉN DEL GENERAL CARLOS I</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>16832.25</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/aysen.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/aysen.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M47"/>
+  <dimension ref="A1:M51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t xml:space="preserve">I. Municipalidad de O'Higgins </t>
+          <t>I MUNICIPALIDAD DE O HIGGINS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -1982,7 +1982,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>1233615-335-CM26</t>
+          <t>1233615-337-CM26</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2022,12 +2022,12 @@
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K26" t="inlineStr"/>
@@ -2037,13 +2037,13 @@
         </is>
       </c>
       <c r="M26" s="2" t="n">
-        <v>2000.99</v>
+        <v>428.4</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>1233615-336-CM26</t>
+          <t>1233615-335-CM26</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2083,12 +2083,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>76.367.430-4</t>
         </is>
       </c>
       <c r="K27" t="inlineStr"/>
@@ -2098,13 +2098,13 @@
         </is>
       </c>
       <c r="M27" s="2" t="n">
-        <v>4665.34</v>
+        <v>2000.99</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>1233615-337-CM26</t>
+          <t>1233615-336-CM26</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
@@ -2159,7 +2159,7 @@
         </is>
       </c>
       <c r="M28" s="2" t="n">
-        <v>428.4</v>
+        <v>4665.34</v>
       </c>
     </row>
     <row r="29">
@@ -2205,7 +2205,7 @@
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2388,7 +2388,7 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TECNOIMPORT SPA</t>
+          <t>comercializadora TecnoImport SpA</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
@@ -2673,7 +2673,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -3039,7 +3039,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Servicio Nacional de Pesca y Acuicultura</t>
+          <t>SERV NACIONAL DE PESCA</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3319,6 +3319,250 @@
       </c>
       <c r="M47" s="2" t="n">
         <v>16832.25</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>1531-30-CM26</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>60.511.112-2</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE GENERAL CARRERA</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>3152.31</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>1415-45-CM26</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>60.511.111-4</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE AYSÉN</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>3148.74</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>1608-92-CM26</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>60.511.110-6</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL REGIONAL DE AYSÉN DEL GENERAL CARLOS IBÁÑEZ DE</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>Sumatec Ltda.</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>3148.74</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>1405-47-CM26</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2239-5-LR25</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>60.511.113-0</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>DELEGACIÓN PRESIDENCIAL PROVINCIAL DE CAPITÁN PRAT</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Aysén</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>RICOH</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>96.513.980-k</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>3152.31</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/aysen.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/aysen.xlsx
@@ -562,7 +562,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +688,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +753,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -806,7 +818,11 @@
           <t>77.108.316-1</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
@@ -867,7 +883,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -928,7 +948,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -989,7 +1013,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1050,7 +1078,11 @@
           <t>76.423.634-3</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1172,7 +1204,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1233,7 +1269,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1294,7 +1334,11 @@
           <t>76.416.101-7</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1420,7 +1464,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1481,7 +1529,11 @@
           <t>77.474.803-2</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1542,7 +1594,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1603,7 +1659,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1664,7 +1724,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1725,7 +1789,11 @@
           <t>76.128.275-1</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1786,7 +1854,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr"/>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L22" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1847,7 +1919,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L23" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1908,7 +1984,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L24" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1969,7 +2049,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L25" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2030,7 +2114,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr"/>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L26" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2152,7 +2240,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr"/>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L28" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2213,7 +2305,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L29" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2396,7 +2492,11 @@
           <t>77.168.105-0</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr"/>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L32" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2457,7 +2557,11 @@
           <t>78.114.650-1</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr"/>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L33" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2640,7 +2744,11 @@
           <t>76.799.430-3</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr"/>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L36" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2701,7 +2809,11 @@
           <t>96.678.350-8</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr"/>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L37" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2762,7 +2874,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr"/>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L38" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2823,7 +2939,11 @@
           <t>77.700.780-7</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr"/>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L39" t="inlineStr">
         <is>
           <t>USD</t>
@@ -2884,7 +3004,11 @@
           <t>96.523.180-3</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr"/>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>Los Lagos</t>
+        </is>
+      </c>
       <c r="L40" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3006,7 +3130,11 @@
           <t>78.112.170-3</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr"/>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L42" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3067,7 +3195,11 @@
           <t>77.727.285-3</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr"/>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L43" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3128,7 +3260,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr"/>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L44" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3250,7 +3386,11 @@
           <t>79.808.810-6</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr"/>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L46" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3311,7 +3451,11 @@
           <t>76.977.985-K</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L47" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3372,7 +3516,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L48" t="inlineStr">
         <is>
           <t>USD</t>
@@ -3555,7 +3703,11 @@
           <t>96.513.980-k</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L51" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/aysen.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/aysen.xlsx
@@ -3488,7 +3488,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">

--- a/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/aysen.xlsx
+++ b/docs/oc-regiones/venta-y-arriendo-de-computadores-y-accesorios/aysen.xlsx
@@ -2976,7 +2976,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
